--- a/data/trans_dic/P38B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,98; 85,7</t>
+          <t>80,04; 85,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,61; 86,36</t>
+          <t>80,33; 86,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,52; 90,62</t>
+          <t>82,26; 90,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,55; 88,81</t>
+          <t>83,63; 88,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,97; 90,14</t>
+          <t>85,15; 90,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,48; 94,21</t>
+          <t>90,66; 94,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,53; 86,41</t>
+          <t>82,7; 86,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,73; 87,69</t>
+          <t>83,66; 87,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,21; 91,83</t>
+          <t>87,43; 91,83</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,02; 83,88</t>
+          <t>78,66; 83,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,8; 84,68</t>
+          <t>79,3; 84,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,05; 78,92</t>
+          <t>29,34; 78,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,26; 88,49</t>
+          <t>84,23; 88,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,89; 92,38</t>
+          <t>88,86; 92,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,28; 86,71</t>
+          <t>82,29; 86,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,15; 85,49</t>
+          <t>82,29; 85,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,93; 87,96</t>
+          <t>84,92; 87,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49,08; 82,01</t>
+          <t>48,99; 81,86</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,2; 85,81</t>
+          <t>80,1; 85,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,22; 84,12</t>
+          <t>77,74; 84,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,18; 83,56</t>
+          <t>75,42; 83,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,74; 92,21</t>
+          <t>87,51; 92,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,85; 90,41</t>
+          <t>85,61; 90,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,66; 94,58</t>
+          <t>85,52; 95,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,95; 88,45</t>
+          <t>85,05; 88,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82,63; 86,42</t>
+          <t>82,9; 86,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,94; 90,11</t>
+          <t>82,25; 90,68</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,64; 83,93</t>
+          <t>78,9; 83,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,24; 83,31</t>
+          <t>78,21; 83,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,98; 83,59</t>
+          <t>76,99; 83,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,23; 90,19</t>
+          <t>85,99; 90,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,74; 85,39</t>
+          <t>80,76; 85,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,4; 88,09</t>
+          <t>65,21; 88,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,41; 86,62</t>
+          <t>83,31; 86,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,39; 83,89</t>
+          <t>80,28; 83,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,65; 84,75</t>
+          <t>70,78; 84,71</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,74; 83,42</t>
+          <t>80,79; 83,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80,45; 83,16</t>
+          <t>80,42; 83,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,8; 81,59</t>
+          <t>57,56; 81,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,58; 88,89</t>
+          <t>86,6; 88,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,37; 88,53</t>
+          <t>86,3; 88,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,36; 88,93</t>
+          <t>80,89; 88,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,15; 85,87</t>
+          <t>84,08; 85,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,85; 85,63</t>
+          <t>83,83; 85,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,59; 84,8</t>
+          <t>70,31; 84,79</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>561887; 602030</t>
+          <t>562305; 600444</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>541689; 580327</t>
+          <t>539816; 578999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>524353; 575854</t>
+          <t>522729; 574102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>577804; 614184</t>
+          <t>578387; 614357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>569227; 603817</t>
+          <t>570385; 604162</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>609268; 634381</t>
+          <t>610498; 635141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1150542; 1204686</t>
+          <t>1152991; 1204101</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1123498; 1176681</t>
+          <t>1122579; 1174422</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1141377; 1201855</t>
+          <t>1144277; 1201861</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>800353; 849508</t>
+          <t>796703; 848369</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>807173; 856532</t>
+          <t>802070; 853757</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>394021; 940808</t>
+          <t>349782; 940343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>866083; 909650</t>
+          <t>865787; 910297</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>925337; 961670</t>
+          <t>925122; 961860</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>788234; 830635</t>
+          <t>788330; 832206</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1676463; 1744538</t>
+          <t>1679293; 1745107</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1743281; 1805401</t>
+          <t>1743002; 1803945</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1055236; 1763192</t>
+          <t>1053257; 1759997</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>600492; 642479</t>
+          <t>599681; 642615</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>586187; 630374</t>
+          <t>582584; 630359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>529003; 587992</t>
+          <t>530723; 588338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>676468; 710869</t>
+          <t>674646; 710220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>672320; 708009</t>
+          <t>670371; 706330</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>799031; 882268</t>
+          <t>797771; 887302</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1291003; 1344087</t>
+          <t>1292546; 1342650</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1266211; 1324422</t>
+          <t>1270381; 1327678</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1341006; 1474602</t>
+          <t>1345959; 1483981</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>738250; 787971</t>
+          <t>740695; 785531</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>728729; 775865</t>
+          <t>728387; 776843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>713492; 774714</t>
+          <t>713533; 774205</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>903723; 945131</t>
+          <t>901129; 946121</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>839467; 887762</t>
+          <t>839641; 887616</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>726560; 963935</t>
+          <t>713540; 963912</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1657202; 1721043</t>
+          <t>1655205; 1719771</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1584495; 1653409</t>
+          <t>1582383; 1650093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1407744; 1712845</t>
+          <t>1430521; 1712024</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2747559; 2838568</t>
+          <t>2749310; 2837390</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2706648; 2797584</t>
+          <t>2705454; 2799000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1998847; 2821310</t>
+          <t>1990444; 2821953</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3063703; 3145389</t>
+          <t>3064325; 3144046</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3052190; 3128441</t>
+          <t>3049687; 3126251</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2976473; 3253470</t>
+          <t>2959067; 3249668</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5841085; 5960478</t>
+          <t>5836035; 5956632</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5783798; 5906573</t>
+          <t>5782206; 5902103</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5094912; 6034595</t>
+          <t>5003784; 6034223</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,04; 85,47</t>
+          <t>80,15; 85,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,33; 86,17</t>
+          <t>80,59; 86,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,26; 90,35</t>
+          <t>82,93; 89,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,63; 88,83</t>
+          <t>83,83; 88,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,15; 90,19</t>
+          <t>85,41; 90,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,66; 94,32</t>
+          <t>89,62; 93,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,7; 86,37</t>
+          <t>82,46; 86,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,66; 87,52</t>
+          <t>83,7; 87,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,43; 91,83</t>
+          <t>87,05; 91,05</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,66; 83,77</t>
+          <t>78,65; 83,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,3; 84,41</t>
+          <t>79,6; 84,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,34; 78,88</t>
+          <t>74,09; 80,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,23; 88,56</t>
+          <t>83,98; 88,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,86; 92,39</t>
+          <t>88,82; 92,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,29; 86,87</t>
+          <t>82,2; 86,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,29; 85,51</t>
+          <t>82,09; 85,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,92; 87,89</t>
+          <t>85,01; 88,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,99; 81,86</t>
+          <t>78,98; 82,85</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,1; 85,83</t>
+          <t>80,21; 86,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,74; 84,12</t>
+          <t>78,21; 84,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,42; 83,61</t>
+          <t>74,03; 82,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,51; 92,12</t>
+          <t>88,08; 92,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,61; 90,2</t>
+          <t>85,83; 90,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,52; 95,12</t>
+          <t>83,28; 88,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,05; 88,35</t>
+          <t>84,92; 88,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82,9; 86,64</t>
+          <t>82,77; 86,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,25; 90,68</t>
+          <t>79,88; 84,57</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,9; 83,67</t>
+          <t>78,97; 83,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,21; 83,41</t>
+          <t>78,36; 83,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,99; 83,53</t>
+          <t>75,83; 82,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,99; 90,28</t>
+          <t>86,3; 90,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,76; 85,38</t>
+          <t>80,74; 85,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,21; 88,09</t>
+          <t>83,85; 88,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,31; 86,56</t>
+          <t>83,19; 86,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,28; 83,72</t>
+          <t>80,34; 83,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,78; 84,71</t>
+          <t>80,84; 84,57</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,79; 83,38</t>
+          <t>80,77; 83,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80,42; 83,2</t>
+          <t>80,48; 83,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,56; 81,61</t>
+          <t>78,27; 81,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,6; 88,85</t>
+          <t>86,55; 88,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,3; 88,47</t>
+          <t>86,23; 88,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,89; 88,83</t>
+          <t>85,51; 87,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,08; 85,81</t>
+          <t>84,18; 85,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,83; 85,56</t>
+          <t>83,79; 85,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,31; 84,79</t>
+          <t>82,29; 84,51</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>554465</t>
+          <t>599292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>624179</t>
+          <t>670231</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1178643</t>
+          <t>1269522</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>562305; 600444</t>
+          <t>563080; 601442</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>539816; 578999</t>
+          <t>541510; 580414</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>522729; 574102</t>
+          <t>572782; 620477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>578387; 614357</t>
+          <t>579808; 615403</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>570385; 604162</t>
+          <t>572137; 604430</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>610498; 635141</t>
+          <t>654702; 684679</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1152991; 1204101</t>
+          <t>1149600; 1206549</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1122579; 1174422</t>
+          <t>1123149; 1175389</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1144277; 1201861</t>
+          <t>1237231; 1294057</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>738415</t>
+          <t>809226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>811868</t>
+          <t>902694</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1550283</t>
+          <t>1711921</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>796703; 848369</t>
+          <t>796559; 848551</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>802070; 853757</t>
+          <t>805170; 854403</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>349782; 940343</t>
+          <t>776359; 840618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>865787; 910297</t>
+          <t>863200; 908514</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>925122; 961860</t>
+          <t>924710; 961842</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>788330; 832206</t>
+          <t>879629; 925506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1679293; 1745107</t>
+          <t>1675246; 1746664</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1743002; 1803945</t>
+          <t>1744953; 1806241</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1053257; 1759997</t>
+          <t>1672857; 1754836</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561307</t>
+          <t>629942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>836650</t>
+          <t>699407</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1397957</t>
+          <t>1329348</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>599681; 642615</t>
+          <t>600527; 644597</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>582584; 630359</t>
+          <t>586112; 629593</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>530723; 588338</t>
+          <t>593814; 658461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>674646; 710220</t>
+          <t>679058; 711205</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>670371; 706330</t>
+          <t>672109; 706421</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>797771; 887302</t>
+          <t>675942; 720394</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1292546; 1342650</t>
+          <t>1290494; 1344398</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1270381; 1327678</t>
+          <t>1268490; 1325265</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1345959; 1483981</t>
+          <t>1289022; 1364676</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>747059</t>
+          <t>784334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>895106</t>
+          <t>961444</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1642165</t>
+          <t>1745778</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>740695; 785531</t>
+          <t>741405; 785664</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>728387; 776843</t>
+          <t>729761; 777951</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>713533; 774205</t>
+          <t>750783; 813280</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>901129; 946121</t>
+          <t>904411; 945808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>839641; 887616</t>
+          <t>839466; 888126</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>713540; 963912</t>
+          <t>937060; 984732</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1655205; 1719771</t>
+          <t>1652746; 1720856</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1582383; 1650093</t>
+          <t>1583541; 1652136</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1430521; 1712024</t>
+          <t>1703789; 1782396</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2601246</t>
+          <t>2822793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3167804</t>
+          <t>3233776</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5769048</t>
+          <t>6056569</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2749310; 2837390</t>
+          <t>2748463; 2839886</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2705454; 2799000</t>
+          <t>2707488; 2797267</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1990444; 2821953</t>
+          <t>2763611; 2884715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3064325; 3144046</t>
+          <t>3062664; 3142480</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3049687; 3126251</t>
+          <t>3046994; 3125537</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2959067; 3249668</t>
+          <t>3189397; 3278648</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5836035; 5956632</t>
+          <t>5843356; 5955221</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5782206; 5902103</t>
+          <t>5779928; 5893636</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5003784; 6034223</t>
+          <t>5974747; 6136083</t>
         </is>
       </c>
     </row>
